--- a/web/files/港岛-北角-海璇 II.xlsx
+++ b/web/files/港岛-北角-海璇 II.xlsx
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>1492</v>
+        <v>1448</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>59388800</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>39805</v>
+        <v>41014</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -10437,9 +10437,9 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 1492呎 (4+房)
+          <t>A | 1448呎 (4+房)
 $5939万
-$39,805/呎
+$41,014/呎
 (24年-09月-17日)</t>
         </is>
       </c>

--- a/web/files/港岛-北角-海璇 II.xlsx
+++ b/web/files/港岛-北角-海璇 II.xlsx
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>2080</v>
+        <v>2127</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>120000000</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>57692</v>
+        <v>56417</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>2073</v>
+        <v>2122</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>121728096</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>58721</v>
+        <v>57365</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>1111</v>
+        <v>1155</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>55000000</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>49505</v>
+        <v>47619</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>1448</v>
+        <v>1492</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>71616000</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>49459</v>
+        <v>48000</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>1111</v>
+        <v>1155</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>43890000</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>39505</v>
+        <v>38000</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>1448</v>
+        <v>1492</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>56364000</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>38925</v>
+        <v>37777</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>1111</v>
+        <v>1155</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>45362000</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>40830</v>
+        <v>39274</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>1448</v>
+        <v>1492</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>54308800</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>37506</v>
+        <v>36400</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>1448</v>
+        <v>1492</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>59388800</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>41014</v>
+        <v>39805</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>1111</v>
+        <v>1155</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>45380000</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>40846</v>
+        <v>39290</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>1448</v>
+        <v>1492</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>52000000</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>35912</v>
+        <v>34853</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>1111</v>
+        <v>1155</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>43067640</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>38765</v>
+        <v>37288</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>1448</v>
+        <v>1492</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>51479000</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>35552</v>
+        <v>34503</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>1111</v>
+        <v>1155</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>41002500</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>36906</v>
+        <v>35500</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>1448</v>
+        <v>1492</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>52300000</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>36119</v>
+        <v>35054</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>1111</v>
+        <v>1155</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>41658500</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>37496</v>
+        <v>36068</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>1448</v>
+        <v>1492</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>49868000</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>34439</v>
+        <v>33424</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>1111</v>
+        <v>1155</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>39616500</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>35658</v>
+        <v>34300</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>1448</v>
+        <v>1492</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>51528000</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>35586</v>
+        <v>34536</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>1111</v>
+        <v>1155</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>39039000</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>35139</v>
+        <v>33800</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>1448</v>
+        <v>1492</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>48191600</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>33281</v>
+        <v>32300</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>1111</v>
+        <v>1155</v>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>38692500</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>34827</v>
+        <v>33500</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>1448</v>
+        <v>1492</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>47800000</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>33011</v>
+        <v>32038</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>1111</v>
+        <v>1155</v>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>37653000</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>33891</v>
+        <v>32600</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>1448</v>
+        <v>1492</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>51680000</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>35691</v>
+        <v>34638</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>1111</v>
+        <v>1155</v>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>38253600</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>34432</v>
+        <v>33120</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>1448</v>
+        <v>1492</v>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>49400000</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>34116</v>
+        <v>33110</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>1095</v>
+        <v>1139</v>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>42780000</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>39068</v>
+        <v>37559</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="E125" s="4" t="n">
-        <v>1432</v>
+        <v>1476</v>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>46494000</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>32468</v>
+        <v>31500</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
@@ -10336,9 +10336,9 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>A | 2080呎 (4+房)
+          <t>A | 2127呎 (4+房)
 $12000万
-$57,692/呎
+$56,417/呎
 (24年-11月-25日)</t>
         </is>
       </c>
@@ -10352,9 +10352,9 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 2073呎 (4+房)
+          <t>A | 2122呎 (4+房)
 $12173万
-$58,721/呎
+$57,365/呎
 (24年-11月-08日)</t>
         </is>
       </c>
@@ -10368,17 +10368,17 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>A | 1448呎 (4+房)
+          <t>A | 1492呎 (4+房)
 $7162万
-$49,459/呎
+$48,000/呎
 (25年-12月-03日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>B | 1111呎 (3房)
+          <t>B | 1155呎 (3房)
 $5500万
-$49,505/呎
+$47,619/呎
 (25年-05月-09日)</t>
         </is>
       </c>
@@ -10391,17 +10391,17 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 1448呎 (4+房)
+          <t>A | 1492呎 (4+房)
 $5636万
-$38,925/呎
+$37,777/呎
 (24年-10月-07日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>B | 1111呎 (3房)
+          <t>B | 1155呎 (3房)
 $4389万
-$39,505/呎
+$38,000/呎
 (24年-10月-04日)</t>
         </is>
       </c>
@@ -10414,17 +10414,17 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>A | 1448呎 (4+房)
+          <t>A | 1492呎 (4+房)
 $5431万
-$37,506/呎
+$36,400/呎
 (24年-10月-08日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>B | 1111呎 (3房)
+          <t>B | 1155呎 (3房)
 $4536万
-$40,830/呎
+$39,274/呎
 (24年-10月-08日)</t>
         </is>
       </c>
@@ -10437,9 +10437,9 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 1448呎 (4+房)
+          <t>A | 1492呎 (4+房)
 $5939万
-$41,014/呎
+$39,805/呎
 (24年-09月-17日)</t>
         </is>
       </c>
@@ -10460,17 +10460,17 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>A | 1448呎 (4+房)
+          <t>A | 1492呎 (4+房)
 $5200万
-$35,912/呎
+$34,853/呎
 (24年-10月-07日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>B | 1111呎 (3房)
+          <t>B | 1155呎 (3房)
 $4538万
-$40,846/呎
+$39,290/呎
 (24年-10月-04日)</t>
         </is>
       </c>
@@ -10483,17 +10483,17 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>A | 1448呎 (4+房)
+          <t>A | 1492呎 (4+房)
 $5148万
-$35,552/呎
+$34,503/呎
 (24年-09月-24日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>B | 1111呎 (3房)
+          <t>B | 1155呎 (3房)
 $4307万
-$38,765/呎
+$37,288/呎
 (24年-09月-23日)</t>
         </is>
       </c>
@@ -10506,17 +10506,17 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>A | 1448呎 (4+房)
+          <t>A | 1492呎 (4+房)
 $5230万
-$36,119/呎
+$35,054/呎
 (24年-10月-09日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>B | 1111呎 (3房)
+          <t>B | 1155呎 (3房)
 $4100万
-$36,906/呎
+$35,500/呎
 (24年-10月-08日)</t>
         </is>
       </c>
@@ -10529,17 +10529,17 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>A | 1448呎 (4+房)
+          <t>A | 1492呎 (4+房)
 $4987万
-$34,439/呎
+$33,424/呎
 (24年-09月-19日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>B | 1111呎 (3房)
+          <t>B | 1155呎 (3房)
 $4166万
-$37,496/呎
+$36,068/呎
 (24年-09月-27日)</t>
         </is>
       </c>
@@ -10552,17 +10552,17 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>A | 1448呎 (4+房)
+          <t>A | 1492呎 (4+房)
 $5153万
-$35,586/呎
+$34,536/呎
 (24年-10月-18日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>B | 1111呎 (3房)
+          <t>B | 1155呎 (3房)
 $3962万
-$35,658/呎
+$34,300/呎
 (24年-10月-30日)</t>
         </is>
       </c>
@@ -10575,17 +10575,17 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>A | 1448呎 (4+房)
+          <t>A | 1492呎 (4+房)
 $4819万
-$33,281/呎
+$32,300/呎
 (24年-10月-03日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>B | 1111呎 (3房)
+          <t>B | 1155呎 (3房)
 $3904万
-$35,139/呎
+$33,800/呎
 (24年-09月-27日)</t>
         </is>
       </c>
@@ -10598,17 +10598,17 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>A | 1448呎 (4+房)
+          <t>A | 1492呎 (4+房)
 $4780万
-$33,011/呎
+$32,038/呎
 (24年-10月-04日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>B | 1111呎 (3房)
+          <t>B | 1155呎 (3房)
 $3869万
-$34,827/呎
+$33,500/呎
 (24年-09月-16日)</t>
         </is>
       </c>
@@ -10621,17 +10621,17 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>A | 1448呎 (4+房)
+          <t>A | 1492呎 (4+房)
 $5168万
-$35,691/呎
+$34,638/呎
 (24年-10月-16日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>B | 1111呎 (3房)
+          <t>B | 1155呎 (3房)
 $3765万
-$33,891/呎
+$32,600/呎
 (24年-09月-23日)</t>
         </is>
       </c>
@@ -10644,17 +10644,17 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>A | 1448呎 (4+房)
+          <t>A | 1492呎 (4+房)
 $4940万
-$34,116/呎
+$33,110/呎
 (24年-10月-21日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>B | 1111呎 (3房)
+          <t>B | 1155呎 (3房)
 $3825万
-$34,432/呎
+$33,120/呎
 (24年-09月-25日)</t>
         </is>
       </c>
@@ -10667,17 +10667,17 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>A | 1432呎 (4+房)
+          <t>A | 1476呎 (4+房)
 $4649万
-$32,468/呎
+$31,500/呎
 (25年-05月-09日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
         <is>
-          <t>B | 1095呎 (3房)
+          <t>B | 1139呎 (3房)
 $4278万
-$39,068/呎
+$37,559/呎
 (24年-11月-18日)</t>
         </is>
       </c>
